--- a/docs/conta/c12/prueba-excel/prueba-c12-url.xlsx
+++ b/docs/conta/c12/prueba-excel/prueba-c12-url.xlsx
@@ -399,80 +399,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Subcuenta cliente</v>
+        <v>43000990</v>
       </c>
       <c r="B1" t="str">
-        <v>Concepto asiento</v>
+        <v>Prueba C12 · factura normal</v>
       </c>
       <c r="C1" t="str">
-        <v>Nombre</v>
+        <v>CLIENTE PRUEBA C12</v>
       </c>
       <c r="D1" t="str">
-        <v>NIF</v>
+        <v>B00000000</v>
       </c>
       <c r="E1" t="str">
-        <v>Subcuenta ingresos 1</v>
+        <v>70000002</v>
       </c>
       <c r="F1" t="str">
-        <v>Nº factura</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Importe ingresos 1</v>
+        <v>PRB-C12-0001</v>
+      </c>
+      <c r="G1">
+        <v>100</v>
       </c>
       <c r="H1" t="str">
-        <v>Subcuenta ingresos 2</v>
+        <v/>
       </c>
       <c r="I1" t="str">
-        <v>Importe ingresos 2</v>
+        <v/>
       </c>
       <c r="J1" t="str">
-        <v>Ruta documento</v>
+        <v/>
       </c>
       <c r="K1" t="str">
-        <v>Url documento</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
       <c r="L1" t="str">
         <v/>
       </c>
-      <c r="M1" t="str">
-        <v>Base IVA 1</v>
-      </c>
-      <c r="N1" t="str">
-        <v>% IVA 1</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Cuota IVA 1</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Total factura</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Fecha</v>
+      <c r="M1">
+        <v>100</v>
+      </c>
+      <c r="N1">
+        <v>10</v>
+      </c>
+      <c r="O1">
+        <v>10</v>
+      </c>
+      <c r="P1">
+        <v>110</v>
+      </c>
+      <c r="Q1" s="1" t="d">
+        <v>2026-10-24T00:00:00.000Z</v>
       </c>
       <c r="R1" t="str">
-        <v>Base IVA 2</v>
+        <v/>
       </c>
       <c r="S1" t="str">
-        <v>% IVA 2</v>
+        <v/>
       </c>
       <c r="T1" t="str">
-        <v>Cuota IVA 2</v>
+        <v/>
       </c>
       <c r="U1" t="str">
-        <v>Tipo factura rectificativa</v>
+        <v/>
       </c>
       <c r="V1" t="str">
-        <v>Tipo rectificación</v>
+        <v/>
       </c>
       <c r="W1" t="str">
-        <v>Nº factura rectificada</v>
+        <v/>
       </c>
       <c r="X1" t="str">
-        <v>Fecha factura rectificada</v>
+        <v/>
       </c>
     </row>
     <row r="2">
@@ -480,7 +480,7 @@
         <v>43000990</v>
       </c>
       <c r="B2" t="str">
-        <v>Prueba C12 · factura normal</v>
+        <v>Prueba C12 · dos tipos de IVA</v>
       </c>
       <c r="C2" t="str">
         <v>CLIENTE PRUEBA C12</v>
@@ -492,16 +492,16 @@
         <v>70000002</v>
       </c>
       <c r="F2" t="str">
-        <v>PRB-C12-0001</v>
+        <v>PRB-C12-0002</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
+        <v>70500001</v>
+      </c>
+      <c r="I2">
+        <v>50</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -522,19 +522,19 @@
         <v>10</v>
       </c>
       <c r="P2">
-        <v>110</v>
+        <v>170.5</v>
       </c>
       <c r="Q2" s="1" t="d">
         <v>2026-10-24T00:00:00.000Z</v>
       </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v/>
+      <c r="R2">
+        <v>50</v>
+      </c>
+      <c r="S2">
+        <v>21</v>
+      </c>
+      <c r="T2">
+        <v>10.5</v>
       </c>
       <c r="U2" t="str">
         <v/>
@@ -554,7 +554,7 @@
         <v>43000990</v>
       </c>
       <c r="B3" t="str">
-        <v>Prueba C12 · dos tipos de IVA</v>
+        <v>Prueba C12 · rectificativa de PRB-C12-0001</v>
       </c>
       <c r="C3" t="str">
         <v>CLIENTE PRUEBA C12</v>
@@ -566,16 +566,16 @@
         <v>70000002</v>
       </c>
       <c r="F3" t="str">
-        <v>PRB-C12-0002</v>
+        <v>PRB-C12-0003</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H3" t="str">
-        <v>70500001</v>
-      </c>
-      <c r="I3">
-        <v>50</v>
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -587,119 +587,45 @@
         <v/>
       </c>
       <c r="M3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="N3">
         <v>10</v>
       </c>
       <c r="O3">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="P3">
-        <v>170.5</v>
+        <v>-110</v>
       </c>
       <c r="Q3" s="1" t="d">
         <v>2026-10-24T00:00:00.000Z</v>
       </c>
-      <c r="R3">
-        <v>50</v>
-      </c>
-      <c r="S3">
-        <v>21</v>
-      </c>
-      <c r="T3">
-        <v>10.5</v>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
       </c>
       <c r="U3" t="str">
-        <v/>
+        <v>R4</v>
       </c>
       <c r="V3" t="str">
-        <v/>
+        <v>I</v>
       </c>
       <c r="W3" t="str">
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>43000990</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Prueba C12 · rectificativa de PRB-C12-0001</v>
-      </c>
-      <c r="C4" t="str">
-        <v>CLIENTE PRUEBA C12</v>
-      </c>
-      <c r="D4" t="str">
-        <v>B00000000</v>
-      </c>
-      <c r="E4" t="str">
-        <v>70000002</v>
-      </c>
-      <c r="F4" t="str">
-        <v>PRB-C12-0003</v>
-      </c>
-      <c r="G4">
-        <v>-100</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4">
-        <v>-100</v>
-      </c>
-      <c r="N4">
-        <v>10</v>
-      </c>
-      <c r="O4">
-        <v>-10</v>
-      </c>
-      <c r="P4">
-        <v>-110</v>
-      </c>
-      <c r="Q4" s="1" t="d">
-        <v>2026-10-24T00:00:00.000Z</v>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v/>
-      </c>
-      <c r="U4" t="str">
-        <v>R4</v>
-      </c>
-      <c r="V4" t="str">
-        <v>I</v>
-      </c>
-      <c r="W4" t="str">
         <v>PRB-C12-0001</v>
       </c>
-      <c r="X4" s="1" t="d">
+      <c r="X3" s="1" t="d">
         <v>2026-10-24T00:00:00.000Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X3"/>
   </ignoredErrors>
 </worksheet>
 </file>